--- a/output/StructureDefinition-patient-nationality-extension.xlsx
+++ b/output/StructureDefinition-patient-nationality-extension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T18:59:27+03:00</t>
+    <t>2026-03-22T11:14:06+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-patient-nationality-extension.xlsx
+++ b/output/StructureDefinition-patient-nationality-extension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-22T11:14:06+05:30</t>
+    <t>2026-03-22T13:21:26+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-patient-nationality-extension.xlsx
+++ b/output/StructureDefinition-patient-nationality-extension.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="157">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-22T13:21:26+05:30</t>
+    <t>2026-03-25T09:53:08+03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -292,6 +292,9 @@
     <t>Extension.extension</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
@@ -410,6 +413,87 @@
   <si>
     <t xml:space="preserve">Period
 </t>
+  </si>
+  <si>
+    <t>Extension.extension:period.value[x].id</t>
+  </si>
+  <si>
+    <t>Extension.extension.value[x].id</t>
+  </si>
+  <si>
+    <t>Extension.extension:period.value[x].extension</t>
+  </si>
+  <si>
+    <t>Extension.extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>Extension.extension:period.value[x].start</t>
+  </si>
+  <si>
+    <t>Extension.extension.value[x].start</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Starting time with inclusive boundary</t>
+  </si>
+  <si>
+    <t>The start of the period. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
+  </si>
+  <si>
+    <t>Period.start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per-1
+</t>
+  </si>
+  <si>
+    <t>./low</t>
+  </si>
+  <si>
+    <t>Extension.extension:period.value[x].end</t>
+  </si>
+  <si>
+    <t>Extension.extension.value[x].end</t>
+  </si>
+  <si>
+    <t>End time with inclusive boundary, if not ongoing</t>
+  </si>
+  <si>
+    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
+  </si>
+  <si>
+    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
+  </si>
+  <si>
+    <t>If the end of the period is missing, it means that the period is ongoing</t>
+  </si>
+  <si>
+    <t>Period.end</t>
+  </si>
+  <si>
+    <t>./high</t>
   </si>
   <si>
     <t>base64Binary
@@ -727,13 +811,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK16"/>
+  <dimension ref="A1:AK20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="31.125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="25.359375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="37.9921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="32.23046875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.984375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="6.890625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="11.10546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
@@ -1100,7 +1184,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>79</v>
@@ -1115,13 +1199,13 @@
         <v>77</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1160,19 +1244,19 @@
         <v>77</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
@@ -1192,13 +1276,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>77</v>
@@ -1220,13 +1304,13 @@
         <v>77</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1277,7 +1361,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -1297,10 +1381,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1400,10 +1484,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1426,13 +1510,13 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1471,19 +1555,19 @@
         <v>77</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -1503,10 +1587,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1529,16 +1613,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1546,7 +1630,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>77</v>
@@ -1588,7 +1672,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>84</v>
@@ -1603,15 +1687,15 @@
         <v>77</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1634,13 +1718,13 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1667,11 +1751,11 @@
         <v>77</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y9" s="2"/>
       <c r="Z9" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>77</v>
@@ -1689,7 +1773,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -1701,28 +1785,28 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>84</v>
@@ -1737,13 +1821,13 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1794,7 +1878,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -1814,10 +1898,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1917,10 +2001,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1943,13 +2027,13 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>32</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1988,19 +2072,19 @@
         <v>77</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2020,10 +2104,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2046,16 +2130,16 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2063,7 +2147,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>77</v>
@@ -2105,7 +2189,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>84</v>
@@ -2120,15 +2204,15 @@
         <v>77</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2151,13 +2235,13 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2208,7 +2292,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2220,18 +2304,18 @@
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2239,7 +2323,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>84</v>
@@ -2254,24 +2338,22 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="S15" t="s" s="2">
         <v>77</v>
@@ -2313,10 +2395,10 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>84</v>
@@ -2328,26 +2410,26 @@
         <v>77</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>77</v>
@@ -2359,15 +2441,17 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>129</v>
+        <v>92</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -2404,34 +2488,454 @@
         <v>77</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O17" s="2"/>
+      <c r="P17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O18" s="2"/>
+      <c r="P18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q18" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="R18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="AK16" t="s" s="2">
-        <v>111</v>
+      <c r="B20" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
